--- a/internal_doc/05.测试设计/story/民生银行资源管控/Story-民生银行资源管控测试用例（资源监控-CL_CL_DETAIL_INFO）.xlsx
+++ b/internal_doc/05.测试设计/story/民生银行资源管控/Story-民生银行资源管控测试用例（资源监控-CL_CL_DETAIL_INFO）.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="38">
   <si>
     <t>name</t>
   </si>
@@ -98,97 +98,91 @@
 3、PG已创建外表并跟sdb中该CL有做映射，且PG跟sdb连接正常</t>
   </si>
   <si>
+    <t>CollectionSpace，检查字段名、类型、字段值正确性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DetailsID，检查字段名、类型、字段值正确性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DetailsLogicalID，检查字段名、类型、字段值正确性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DetailsSequence，检查字段名、类型、字段值正确性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DetailsIndexes，检查字段名、类型、字段值正确性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DetailsStatus，检查字段名、类型、字段值正确性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DetailsTotalRecords，检查字段名、类型、字段值正确性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DetailsTotalDataPages，检查字段名、类型、字段值正确性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DetailsTotalIndexPages，检查字段名、类型、字段值正确性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DetailsTotalLobPages，检查字段名、类型、字段值正确性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DetailsTotalDataFreeSpace，检查字段名、类型、字段值正确性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DetailsTotalIndexFreeSpace，检查字段名、类型、字段值正确性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>1、检查CL中该字段名、类型是否符合接口文档设计规范 
-2、检查CL中字段值跟sdb.snapshot(4)快照信息是否一致</t>
+2、检查CL中字段值跟db.snapshot(4)快照信息是否一致</t>
+  </si>
+  <si>
+    <t>1. 字段名命名定义与接口文档定义的一致
+2、字段类型为“字符串”，与接口文档定义的一致
+3、字段值与实际db.snapshot(4)查询的该字段信息一致</t>
   </si>
   <si>
     <t>1、检查CL中该字段名、类型是否符合接口文档设计规范 
-2、检查CL中字段值跟sdb.snapshot(4)快照信息是否一致，覆盖如下取值：
+2、检查CL中字段值跟db.snapshot(4)快照信息是否一致，覆盖如下取值：
   0：直连服务，对应数据库参数 svcname
   1：复制服务，对应数据库参数 replname
   2：分区服务，对应数据库参数 shardname
   3：编目服务，对应数据库参数 catalogname</t>
   </si>
   <si>
+    <t>1. 字段名命名定义与接口文档定义的一致
+2、字段类型为“整型”，与接口文档定义的一致
+3、字段值与实际db.snapshot(4)查询的该字段信息一致</t>
+  </si>
+  <si>
     <t>1、检查CL中该字段名、类型是否符合接口文档设计规范 
-2、检查CL中字段值跟sdb.snapshot(4)快照信息是否一致，覆盖如下取值：
+2、检查CL中字段值跟db.snapshot(4)快照信息是否一致，覆盖如下取值：
   服务名为端口号
   services文件中的服务名</t>
   </si>
   <si>
+    <t>1. 字段名命名定义与接口文档定义的一致
+2、字段类型为“长整型”，与接口文档定义的一致
+3、字段值与实际db.snapshot(4)查询的该字段信息一致</t>
+  </si>
+  <si>
     <t>1、检查CL中该字段名、类型是否符合接口文档设计规范 
-2、检查CL中字段值跟sdb.snapshot(4)快照信息是否一致，覆盖如下取值：
+2、检查CL中字段值跟db.snapshot(4)快照信息是否一致，覆盖如下取值：
   0：数据节点
   2：编目节点</t>
-  </si>
-  <si>
-    <t>1、检查CL中该字段名、类型是否符合接口文档设计规范 
-2、检查CL中字段值跟sdb.snapshot(4)快照信息是否一致</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 字段名命名定义与接口文档定义的一致
-2、字段类型为“字符串”，与接口文档定义的一致
-3、字段值与实际sdb.snapshot(4)查询的该字段信息一致</t>
-  </si>
-  <si>
-    <t>1. 字段名命名定义与接口文档定义的一致
-2、字段类型为“整型”，与接口文档定义的一致
-3、字段值与实际sdb.snapshot(4)查询的该字段信息一致</t>
-  </si>
-  <si>
-    <t>CollectionSpace，检查字段名、类型、字段值正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DetailsID，检查字段名、类型、字段值正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DetailsLogicalID，检查字段名、类型、字段值正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DetailsSequence，检查字段名、类型、字段值正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DetailsIndexes，检查字段名、类型、字段值正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DetailsStatus，检查字段名、类型、字段值正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DetailsTotalRecords，检查字段名、类型、字段值正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DetailsTotalDataPages，检查字段名、类型、字段值正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DetailsTotalIndexPages，检查字段名、类型、字段值正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DetailsTotalLobPages，检查字段名、类型、字段值正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DetailsTotalDataFreeSpace，检查字段名、类型、字段值正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DetailsTotalIndexFreeSpace，检查字段名、类型、字段值正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 字段名命名定义与接口文档定义的一致
-2、字段类型为“长整型”，与接口文档定义的一致
-3、字段值与实际sdb.snapshot(4)查询的该字段信息一致</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -716,10 +710,10 @@
         <v>1</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I2" s="3">
         <v>1</v>
@@ -727,7 +721,7 @@
     </row>
     <row r="3" spans="1:9" ht="81">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -742,10 +736,10 @@
         <v>1</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I3" s="3">
         <v>1</v>
@@ -753,7 +747,7 @@
     </row>
     <row r="4" spans="1:9" ht="94.5">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>16</v>
@@ -768,10 +762,10 @@
         <v>1</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="I4" s="3">
         <v>1</v>
@@ -779,7 +773,7 @@
     </row>
     <row r="5" spans="1:9" ht="81">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>16</v>
@@ -794,10 +788,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I5" s="3">
         <v>1</v>
@@ -805,7 +799,7 @@
     </row>
     <row r="6" spans="1:9" ht="81">
       <c r="A6" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>16</v>
@@ -820,10 +814,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="I6" s="3">
         <v>1</v>
@@ -831,7 +825,7 @@
     </row>
     <row r="7" spans="1:9" ht="81">
       <c r="A7" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>16</v>
@@ -846,10 +840,10 @@
         <v>1</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="I7" s="3">
         <v>1</v>
@@ -857,25 +851,25 @@
     </row>
     <row r="8" spans="1:9" ht="81">
       <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="3">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3">
-        <v>2</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="H8" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I8" s="3">
         <v>1</v>
@@ -883,7 +877,7 @@
     </row>
     <row r="9" spans="1:9" ht="81">
       <c r="A9" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>16</v>
@@ -898,10 +892,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I9" s="3">
         <v>1</v>
@@ -909,7 +903,7 @@
     </row>
     <row r="10" spans="1:9" ht="81">
       <c r="A10" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>16</v>
@@ -924,10 +918,10 @@
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="I10" s="3">
         <v>1</v>
@@ -935,25 +929,25 @@
     </row>
     <row r="11" spans="1:9" ht="81">
       <c r="A11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3">
+        <v>2</v>
+      </c>
+      <c r="F11" s="3">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="3">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3">
-        <v>2</v>
-      </c>
-      <c r="F11" s="3">
-        <v>1</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="I11" s="3">
         <v>1</v>
@@ -961,7 +955,7 @@
     </row>
     <row r="12" spans="1:9" ht="81">
       <c r="A12" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>16</v>
@@ -976,10 +970,10 @@
         <v>1</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="I12" s="3">
         <v>1</v>
@@ -987,25 +981,25 @@
     </row>
     <row r="13" spans="1:9" ht="81">
       <c r="A13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3">
+        <v>2</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="3">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3">
-        <v>2</v>
-      </c>
-      <c r="F13" s="3">
-        <v>1</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="I13" s="3">
         <v>1</v>
@@ -1013,7 +1007,7 @@
     </row>
     <row r="14" spans="1:9" ht="81">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>16</v>
@@ -1028,10 +1022,10 @@
         <v>1</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I14" s="3">
         <v>1</v>
